--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M234"/>
+  <dimension ref="A1:M232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>811299.9300000001</v>
+        <v>917.8</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>299250.13</v>
+        <v>338.53</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2717722</v>
+        <v>3074.47</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3510202.5</v>
+        <v>3970.97</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>66211199.74</v>
+        <v>74902.45</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>27882691.57</v>
+        <v>31542.73</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9044000</v>
+        <v>10231.17</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>57598500.19</v>
+        <v>65159.2</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14999474</v>
+        <v>16968.39</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>99854.48</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>29489171.64</v>
+        <v>33360.09</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>26001500</v>
+        <v>29414.6</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6312821.66</v>
+        <v>7141.48</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1999999.76004628</v>
+        <v>2262.53</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>209000.06</v>
+        <v>236.43</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6783000</v>
+        <v>7673.37</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12790134.46</v>
+        <v>14469.04</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>71249999.91</v>
+        <v>80602.67</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>999999.6</v>
+        <v>1131.27</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>28001483.38</v>
+        <v>31677.12</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>26600000.27</v>
+        <v>30091.67</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5510851.74</v>
+        <v>6234.24</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>46279250.24</v>
+        <v>52354.12</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7999999.08</v>
+        <v>9050.120000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>44103749.95</v>
+        <v>49893.06</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>62358380</v>
+        <v>70543.89</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5705271.44</v>
+        <v>6454.18</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>480000.13</v>
+        <v>543.01</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>14696500</v>
+        <v>16625.65</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11500576.5</v>
+        <v>13010.21</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12948499.42</v>
+        <v>14648.19</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>604200.25</v>
+        <v>683.51</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>364799.91</v>
+        <v>412.69</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9894250.18</v>
+        <v>11193.03</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7557250.06</v>
+        <v>8549.26</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>483549.9</v>
+        <v>547.02</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>707749.53</v>
+        <v>800.65</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1382724.72</v>
+        <v>1564.23</v>
       </c>
     </row>
     <row r="40">
@@ -2887,11 +2887,11 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>230843392.36</v>
+        <v>261145.19</v>
       </c>
     </row>
     <row r="41">
@@ -2948,11 +2948,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19317964.78</v>
+        <v>21853.75</v>
       </c>
     </row>
     <row r="42">
@@ -3009,11 +3009,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>19478801.02</v>
+        <v>22035.7</v>
       </c>
     </row>
     <row r="43">
@@ -3070,11 +3070,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14249999.98</v>
+        <v>16120.53</v>
       </c>
     </row>
     <row r="44">
@@ -3131,11 +3131,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>13947899.86</v>
+        <v>15778.78</v>
       </c>
     </row>
     <row r="45">
@@ -3192,11 +3192,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>23417500.32</v>
+        <v>26491.41</v>
       </c>
     </row>
     <row r="46">
@@ -3253,11 +3253,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7801875.56</v>
+        <v>8825.99</v>
       </c>
     </row>
     <row r="47">
@@ -3314,11 +3314,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>9761401.73</v>
+        <v>11042.74</v>
       </c>
     </row>
     <row r="48">
@@ -3375,11 +3375,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>6974999.6</v>
+        <v>7890.58</v>
       </c>
     </row>
     <row r="49">
@@ -3436,11 +3436,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>21702750.01</v>
+        <v>24551.57</v>
       </c>
     </row>
     <row r="50">
@@ -3497,11 +3497,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26566750</v>
+        <v>30054.05</v>
       </c>
     </row>
     <row r="51">
@@ -3558,11 +3558,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8663999.380000001</v>
+        <v>9801.280000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3619,11 +3619,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8747917.850046281</v>
+        <v>9896.219999999999</v>
       </c>
     </row>
     <row r="53">
@@ -3680,11 +3680,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2438801.65</v>
+        <v>2758.93</v>
       </c>
     </row>
     <row r="54">
@@ -3741,11 +3741,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>170049.81</v>
+        <v>192.37</v>
       </c>
     </row>
     <row r="55">
@@ -3802,11 +3802,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8478750</v>
+        <v>9591.719999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3863,11 +3863,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1130400</v>
+        <v>1278.78</v>
       </c>
     </row>
     <row r="57">
@@ -3924,11 +3924,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6788699.98</v>
+        <v>7679.82</v>
       </c>
     </row>
     <row r="58">
@@ -3985,11 +3985,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>64124999.91</v>
+        <v>72542.41</v>
       </c>
     </row>
     <row r="59">
@@ -4046,11 +4046,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>13489999.88</v>
+        <v>15260.77</v>
       </c>
     </row>
     <row r="60">
@@ -4107,11 +4107,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2507999.55</v>
+        <v>2837.21</v>
       </c>
     </row>
     <row r="61">
@@ -4168,11 +4168,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>29888062.16</v>
+        <v>33811.34</v>
       </c>
     </row>
     <row r="62">
@@ -4229,11 +4229,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3231743.39</v>
+        <v>3655.96</v>
       </c>
     </row>
     <row r="63">
@@ -4290,11 +4290,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>13000000.48</v>
+        <v>14706.45</v>
       </c>
     </row>
     <row r="64">
@@ -4351,11 +4351,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>325374.86</v>
+        <v>368.09</v>
       </c>
     </row>
     <row r="65">
@@ -4412,11 +4412,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>42210874.67</v>
+        <v>47751.71</v>
       </c>
     </row>
     <row r="66">
@@ -4473,11 +4473,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>18023399.84</v>
+        <v>20389.25</v>
       </c>
     </row>
     <row r="67">
@@ -4534,11 +4534,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>38889200</v>
+        <v>43994.01</v>
       </c>
     </row>
     <row r="68">
@@ -4595,11 +4595,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>42863999.56</v>
+        <v>48490.57</v>
       </c>
     </row>
     <row r="69">
@@ -4656,11 +4656,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>62141399.74</v>
+        <v>70298.42999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4717,11 +4717,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>570000.36</v>
+        <v>644.8200000000001</v>
       </c>
     </row>
     <row r="71">
@@ -4778,11 +4778,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>38285000.88</v>
+        <v>43310.51</v>
       </c>
     </row>
     <row r="72">
@@ -4839,11 +4839,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>46378703.71</v>
+        <v>52466.63</v>
       </c>
     </row>
     <row r="73">
@@ -4900,11 +4900,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10463908</v>
+        <v>11837.46</v>
       </c>
     </row>
     <row r="74">
@@ -4961,11 +4961,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>10679999.68</v>
+        <v>12081.92</v>
       </c>
     </row>
     <row r="75">
@@ -5022,11 +5022,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7757700.14</v>
+        <v>8776.02</v>
       </c>
     </row>
     <row r="76">
@@ -5083,11 +5083,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>60000000.99</v>
+        <v>67875.94</v>
       </c>
     </row>
     <row r="77">
@@ -5144,11 +5144,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22200000.43</v>
+        <v>25114.1</v>
       </c>
     </row>
     <row r="78">
@@ -5205,11 +5205,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2107908.88</v>
+        <v>2384.6</v>
       </c>
     </row>
     <row r="79">
@@ -5266,11 +5266,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8985289.74</v>
+        <v>10164.75</v>
       </c>
     </row>
     <row r="80">
@@ -5327,11 +5327,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>20914250</v>
+        <v>23659.57</v>
       </c>
     </row>
     <row r="81">
@@ -5388,11 +5388,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9670022.289999999</v>
+        <v>10939.36</v>
       </c>
     </row>
     <row r="82">
@@ -5449,11 +5449,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5878125.19</v>
+        <v>6649.72</v>
       </c>
     </row>
     <row r="83">
@@ -5510,11 +5510,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>9063000.310000001</v>
+        <v>10252.66</v>
       </c>
     </row>
     <row r="84">
@@ -5571,11 +5571,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>35000000.77</v>
+        <v>39594.3</v>
       </c>
     </row>
     <row r="85">
@@ -5632,11 +5632,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>6759250.46</v>
+        <v>7646.51</v>
       </c>
     </row>
     <row r="86">
@@ -5693,11 +5693,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>17063044.61</v>
+        <v>19302.84</v>
       </c>
     </row>
     <row r="87">
@@ -5754,11 +5754,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>99854.48</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="88">
@@ -5815,11 +5815,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>33553999.7</v>
+        <v>37958.49</v>
       </c>
     </row>
     <row r="89">
@@ -5876,11 +5876,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8500000.01</v>
+        <v>9615.76</v>
       </c>
     </row>
     <row r="90">
@@ -5937,11 +5937,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11323999.18</v>
+        <v>12810.45</v>
       </c>
     </row>
     <row r="91">
@@ -5998,11 +5998,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>11000000.14</v>
+        <v>12443.92</v>
       </c>
     </row>
     <row r="92">
@@ -6059,11 +6059,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1199999.75</v>
+        <v>1357.52</v>
       </c>
     </row>
     <row r="93">
@@ -6120,11 +6120,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5000000.27</v>
+        <v>5656.33</v>
       </c>
     </row>
     <row r="94">
@@ -6181,11 +6181,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2000808</v>
+        <v>2263.45</v>
       </c>
     </row>
     <row r="95">
@@ -6242,11 +6242,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>10174500</v>
+        <v>11510.06</v>
       </c>
     </row>
     <row r="96">
@@ -6303,11 +6303,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2637503.98</v>
+        <v>2983.72</v>
       </c>
     </row>
     <row r="97">
@@ -6364,11 +6364,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4906266.64</v>
+        <v>5550.29</v>
       </c>
     </row>
     <row r="98">
@@ -6425,11 +6425,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3158275.59</v>
+        <v>3572.85</v>
       </c>
     </row>
     <row r="99">
@@ -6486,11 +6486,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1282120.4</v>
+        <v>1450.42</v>
       </c>
     </row>
     <row r="100">
@@ -6547,11 +6547,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10521250.35</v>
+        <v>11902.33</v>
       </c>
     </row>
     <row r="101">
@@ -6608,11 +6608,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8283999.9</v>
+        <v>9371.4</v>
       </c>
     </row>
     <row r="102">
@@ -6669,11 +6669,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7953494.83</v>
+        <v>8997.52</v>
       </c>
     </row>
     <row r="103">
@@ -6730,11 +6730,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>997500.0699999999</v>
+        <v>1128.44</v>
       </c>
     </row>
     <row r="104">
@@ -6791,11 +6791,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>45828485.97</v>
+        <v>51844.19</v>
       </c>
     </row>
     <row r="105">
@@ -6852,11 +6852,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>46523544.5</v>
+        <v>52630.49</v>
       </c>
     </row>
     <row r="106">
@@ -6913,11 +6913,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>156275.8</v>
+        <v>176.79</v>
       </c>
     </row>
     <row r="107">
@@ -6974,11 +6974,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>18000000.75</v>
+        <v>20362.78</v>
       </c>
     </row>
     <row r="108">
@@ -7035,11 +7035,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7329249.69</v>
+        <v>8291.33</v>
       </c>
     </row>
     <row r="109">
@@ -7096,11 +7096,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5814400.04</v>
+        <v>6577.63</v>
       </c>
     </row>
     <row r="110">
@@ -7157,17 +7157,17 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3315501.01</v>
+        <v>3750.71</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1643-134-CM26</t>
+          <t>576152-1-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7187,22 +7187,22 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.602.122-2</t>
+          <t>61.002.002-k</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
+          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7218,11 +7218,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>10769199.53</v>
+        <v>15984.78</v>
       </c>
     </row>
     <row r="112">
@@ -7279,11 +7279,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4925370.31</v>
+        <v>5571.9</v>
       </c>
     </row>
     <row r="113">
@@ -7344,17 +7344,17 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>68315845.1999622</v>
+        <v>77283.37</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>576152-1-CM26</t>
+          <t>1643-134-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7374,22 +7374,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.002.002-k</t>
+          <t>61.602.122-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7405,11 +7405,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>14130000</v>
+        <v>12182.83</v>
       </c>
     </row>
     <row r="115">
@@ -7466,11 +7466,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>9120000.119999999</v>
+        <v>10317.14</v>
       </c>
     </row>
     <row r="116">
@@ -7527,17 +7527,17 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>316839.58</v>
+        <v>358.43</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3431-2-CM26</t>
+          <t>3355-9-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7588,17 +7588,17 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4279999.52</v>
+        <v>2827.64</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3355-10-CM26</t>
+          <t>3431-2-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7649,17 +7649,17 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1000492.5</v>
+        <v>4841.82</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3355-9-CM26</t>
+          <t>3355-10-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7710,17 +7710,17 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2499535.5</v>
+        <v>1131.82</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1057388-27-CM26</t>
+          <t>3220-14-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7771,17 +7771,17 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>12055500.51</v>
+        <v>31372.75</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>898-187-CM26</t>
+          <t>707412-5-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7806,17 +7806,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7832,17 +7832,17 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>19950000.2</v>
+        <v>4745.33</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3347-8-CM26</t>
+          <t>1271436-4-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.101.036-2</t>
+          <t>65.027.349-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION TEATRO MUNICIPAL DE LAS CONDES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,17 +7893,17 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4501651</v>
+        <v>21403.55</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3474-29-CM26</t>
+          <t>1079596-5-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7928,17 +7928,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7954,17 +7954,17 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2487100</v>
+        <v>30100.8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5769-14-CM26</t>
+          <t>1057388-27-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7989,17 +7989,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8015,17 +8015,17 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3927464.4</v>
+        <v>13637.97</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1070329-3-CM26</t>
+          <t>5769-14-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8076,17 +8076,17 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>12503330</v>
+        <v>4443.01</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1079596-5-CM26</t>
+          <t>3474-29-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8111,17 +8111,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8137,17 +8137,17 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>26608075.43</v>
+        <v>2813.57</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1271436-4-CM26</t>
+          <t>3347-8-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>65.027.349-4</t>
+          <t>61.101.036-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FUNDACION TEATRO MUNICIPAL DE LAS CONDES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8198,17 +8198,17 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>18920000</v>
+        <v>5092.56</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>707412-5-CM26</t>
+          <t>898-187-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8233,17 +8233,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8259,17 +8259,17 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4194708.32</v>
+        <v>22568.75</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3220-14-CM26</t>
+          <t>1070329-3-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8320,17 +8320,17 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>27732437.94</v>
+        <v>14144.59</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1503362-1-CM26</t>
+          <t>2013-40-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8350,22 +8350,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8381,17 +8381,17 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>678300</v>
+        <v>859.76</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057514-48-CM26</t>
+          <t>3416-30-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>61.101.017-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8442,17 +8442,17 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>12518624.53</v>
+        <v>3393.68</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1402-14-CM26</t>
+          <t>4820-17-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8472,22 +8472,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8503,17 +8503,17 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3200000.08</v>
+        <v>56563.28</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1402-15-CM26</t>
+          <t>1386073-9-SE26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8533,22 +8533,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>71.004.200-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>CORP CULTURAL DE LAS CONDES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8561,20 +8561,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1100000.24</v>
+        <v>126814.88</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4820-17-CM26</t>
+          <t>1402-14-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8594,22 +8598,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8625,17 +8629,17 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>50000000.45</v>
+        <v>3620.05</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3416-30-CM26</t>
+          <t>1057514-48-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8660,17 +8664,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.101.017-6</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8686,17 +8690,17 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2999893.67</v>
+        <v>14161.89</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2013-40-CM26</t>
+          <t>1402-15-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8716,22 +8720,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8747,17 +8751,17 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>760000.1</v>
+        <v>1244.39</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1386073-9-SE26</t>
+          <t>1503362-1-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8777,22 +8781,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>71.004.200-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LAS CONDES</t>
+          <t>SERVICIO DEL PATRIMONIO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8805,18 +8809,14 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>112100000.39</v>
+        <v>767.34</v>
       </c>
     </row>
     <row r="138">
@@ -8873,11 +8873,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4000000.67</v>
+        <v>4525.06</v>
       </c>
     </row>
     <row r="139">
@@ -8934,11 +8934,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>5878600</v>
+        <v>6650.26</v>
       </c>
     </row>
     <row r="140">
@@ -8995,11 +8995,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>14870031.75</v>
+        <v>16821.96</v>
       </c>
     </row>
     <row r="141">
@@ -9056,11 +9056,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>32000000.83</v>
+        <v>36200.5</v>
       </c>
     </row>
     <row r="142">
@@ -9117,11 +9117,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>237499.96</v>
+        <v>268.68</v>
       </c>
     </row>
     <row r="143">
@@ -9178,11 +9178,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>9999999.41</v>
+        <v>11312.66</v>
       </c>
     </row>
     <row r="144">
@@ -9239,11 +9239,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>16890999.47</v>
+        <v>19108.21</v>
       </c>
     </row>
     <row r="145">
@@ -9300,11 +9300,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4522000</v>
+        <v>5115.58</v>
       </c>
     </row>
     <row r="146">
@@ -9361,17 +9361,17 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>39899999.27</v>
+        <v>45137.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4777-41-CM26</t>
+          <t>1620-21-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9391,22 +9391,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9422,17 +9422,17 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>23487200</v>
+        <v>15837.85</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1620-21-CM26</t>
+          <t>1079580-9-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9457,17 +9457,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SECCIÓN COMPRAS XVI ZONA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9483,17 +9483,17 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>14000112</v>
+        <v>43265.37</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1079580-9-CM26</t>
+          <t>5702-26-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9518,17 +9518,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9544,17 +9544,17 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>38245099.89</v>
+        <v>16968.39</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5702-26-CM26</t>
+          <t>3474-56-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9579,17 +9579,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9605,17 +9605,17 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>14999474</v>
+        <v>1087.06</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3474-56-CM26</t>
+          <t>652-29-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9640,17 +9640,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9666,17 +9666,17 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>960925</v>
+        <v>39147.11</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2568-8-CM26</t>
+          <t>4777-41-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9696,22 +9696,22 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9727,17 +9727,17 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1045000.29</v>
+        <v>26570.26</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>652-29-CM26</t>
+          <t>4777-40-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9757,22 +9757,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9788,17 +9788,17 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>34604699.96</v>
+        <v>10940.7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4777-40-CM26</t>
+          <t>2568-8-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9818,22 +9818,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9849,17 +9849,17 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>9671200</v>
+        <v>1182.17</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>522-12-CM26</t>
+          <t>1043742-2-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9884,17 +9884,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Instituto de Seguridad Laboral</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9910,17 +9910,17 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>22000000.29</v>
+        <v>6787.59</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1043742-2-CM26</t>
+          <t>617807-627-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9945,17 +9945,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9971,17 +9971,17 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6000001</v>
+        <v>18173.22</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>620279-19-CM26</t>
+          <t>1557-13-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10001,22 +10001,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10032,17 +10032,17 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>13473131.69</v>
+        <v>13971.13</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1057506-3628-CM26</t>
+          <t>3233-1-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10062,22 +10062,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.102.026-0</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10093,17 +10093,17 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>24999999.09</v>
+        <v>65148.32</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1079639-16-CM26</t>
+          <t>522-12-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10128,17 +10128,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>HOSPITAL DE LITUECHE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10154,17 +10154,17 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>36182719.69</v>
+        <v>24887.84</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1079639-14-CM26</t>
+          <t>1079639-16-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10215,17 +10215,17 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>38495900.18</v>
+        <v>40932.27</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3233-1-CM26</t>
+          <t>1057506-3628-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10245,22 +10245,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.102.026-0</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10276,17 +10276,17 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>57588877.37</v>
+        <v>28281.64</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1557-13-CM26</t>
+          <t>1079639-14-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10337,17 +10337,17 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>12349998.02</v>
+        <v>43549.09</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>617807-627-CM26</t>
+          <t>1391-175-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10372,17 +10372,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10398,17 +10398,17 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>16064499.96</v>
+        <v>678.76</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2170-62-CM26</t>
+          <t>2170-61-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10459,17 +10459,17 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>7902574.85</v>
+        <v>22729.95</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1057374-56-CM26</t>
+          <t>5911-19-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10494,17 +10494,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>70.819.400-K</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>TRIBUNAL CONSTITUCIONAL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10520,17 +10520,17 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>11341176</v>
+        <v>9856.1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1072229-11-CM26</t>
+          <t>4100-4-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10555,17 +10555,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Dirección General de Carabineros de Chile</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10581,17 +10581,17 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>5868720.56</v>
+        <v>8766.35</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1371-9-CM26</t>
+          <t>3474-58-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10642,17 +10642,17 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>503499.83</v>
+        <v>1550.8</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1622-117-CM26</t>
+          <t>3474-57-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10677,17 +10677,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10703,17 +10703,17 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>23000001.02</v>
+        <v>5587.38</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3474-58-CM26</t>
+          <t>1371-9-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>Comité de Seguro Agricola</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10764,17 +10764,17 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1370849.95</v>
+        <v>569.59</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4100-4-CM26</t>
+          <t>1072229-11-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10799,17 +10799,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10825,17 +10825,17 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>7749150.17</v>
+        <v>6639.08</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5911-19-CM26</t>
+          <t>1057374-56-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10860,17 +10860,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>70.819.400-K</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>TRIBUNAL CONSTITUCIONAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10886,17 +10886,17 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>8712450.35</v>
+        <v>12829.88</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2170-61-CM26</t>
+          <t>2170-62-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10947,17 +10947,17 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>20092499.72</v>
+        <v>8939.91</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3474-57-CM26</t>
+          <t>1622-117-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10982,17 +10982,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11008,17 +11008,17 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4939050.49</v>
+        <v>26019.11</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1391-175-CM26</t>
+          <t>3439-1-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11043,17 +11043,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11069,17 +11069,17 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>600000.4399999999</v>
+        <v>1455.15</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3439-1-CM26</t>
+          <t>418-112-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11104,17 +11104,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11130,17 +11130,17 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1286300.99</v>
+        <v>36529.3</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>418-112-CM26</t>
+          <t>1274667-2-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11191,17 +11191,17 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>32290650.12</v>
+        <v>13575.19</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3951-10-CM26</t>
+          <t>778992-12-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11226,17 +11226,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11252,17 +11252,17 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>6395400.16</v>
+        <v>3836.69</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3951-9-CM26</t>
+          <t>3483-13-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11287,17 +11287,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11313,17 +11313,17 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1016500.38</v>
+        <v>389.16</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1391-149-CM26</t>
+          <t>3326-36-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11348,17 +11348,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11374,17 +11374,17 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1999987.9</v>
+        <v>149.89</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3217-4-CM26</t>
+          <t>1079659-23-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11409,17 +11409,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11435,17 +11435,17 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>21586573.05</v>
+        <v>36990.18</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1057496-173-CM26</t>
+          <t>3217-4-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11470,17 +11470,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.608.105-5</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
+          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11496,17 +11496,17 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5035267.35</v>
+        <v>24420.15</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3326-36-CM26</t>
+          <t>1391-149-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11531,17 +11531,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11557,17 +11557,17 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>132500.25</v>
+        <v>2262.52</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3483-13-CM26</t>
+          <t>3951-9-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11592,17 +11592,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11618,17 +11618,17 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>343999.85</v>
+        <v>1149.93</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>778992-12-CM26</t>
+          <t>3951-10-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11653,17 +11653,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11679,17 +11679,17 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3391500</v>
+        <v>7234.9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1274667-2-CM26</t>
+          <t>1057496-173-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11714,17 +11714,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.608.105-5</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11740,17 +11740,17 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>12000000.88</v>
+        <v>5696.22</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1079659-23-CM26</t>
+          <t>2085-73-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11801,17 +11801,17 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>32698050.67</v>
+        <v>28768.5</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2085-73-CM26</t>
+          <t>1079580-14-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SECCIÓN COMPRAS XVI ZONA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11862,17 +11862,17 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>25430365.75</v>
+        <v>5373.51</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1079580-14-CM26</t>
+          <t>3399-14-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11897,17 +11897,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11923,11 +11923,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4750000.37</v>
+        <v>3325.13</v>
       </c>
     </row>
     <row r="189">
@@ -11984,17 +11984,17 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>36799200.56</v>
+        <v>41629.67</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3399-14-CM26</t>
+          <t>635-60-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12045,17 +12045,17 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2939300</v>
+        <v>45785.81</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1978-70-CM26</t>
+          <t>3374-2-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12080,17 +12080,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12106,17 +12106,17 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>52249999.55</v>
+        <v>2828.16</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>635-60-CM26</t>
+          <t>2045-30-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12141,17 +12141,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12167,17 +12167,17 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>40473083.63</v>
+        <v>9050.129999999999</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3374-2-CM26</t>
+          <t>1978-70-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12202,17 +12202,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12228,17 +12228,17 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2499999.01</v>
+        <v>59108.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2045-30-CM26</t>
+          <t>1383-21-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12253,27 +12253,27 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12289,11 +12289,11 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>8000000.21</v>
+        <v>9229.43</v>
       </c>
     </row>
     <row r="195">
@@ -12350,11 +12350,11 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>20526400.32</v>
+        <v>23220.81</v>
       </c>
     </row>
     <row r="196">
@@ -12411,11 +12411,11 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>28262500</v>
+        <v>31972.39</v>
       </c>
     </row>
     <row r="197">
@@ -12472,11 +12472,11 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>51765973.72</v>
+        <v>58561.07</v>
       </c>
     </row>
     <row r="198">
@@ -12533,11 +12533,11 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>71249999.91</v>
+        <v>80602.67</v>
       </c>
     </row>
     <row r="199">
@@ -12594,11 +12594,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>28499999.96</v>
+        <v>32241.07</v>
       </c>
     </row>
     <row r="200">
@@ -12655,11 +12655,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>389500.21</v>
+        <v>440.63</v>
       </c>
     </row>
     <row r="201">
@@ -12716,11 +12716,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>15000000.81</v>
+        <v>16968.99</v>
       </c>
     </row>
     <row r="202">
@@ -12777,11 +12777,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>24028255.21</v>
+        <v>27182.34</v>
       </c>
     </row>
     <row r="203">
@@ -12838,17 +12838,17 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>7913500</v>
+        <v>8952.27</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1383-21-CM26</t>
+          <t>620279-22-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12873,17 +12873,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>BASE NAVAL PUERTO MONTT</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12899,17 +12899,17 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8158500.83</v>
+        <v>15200.97</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>620279-22-CM26</t>
+          <t>1624-12-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12929,22 +12929,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12960,17 +12960,17 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>13437132.04</v>
+        <v>10103.28</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1624-12-CM26</t>
+          <t>707423-5-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12995,17 +12995,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13021,17 +13021,17 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>8930950</v>
+        <v>662.47</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>707423-5-CM26</t>
+          <t>3047-24-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13051,22 +13051,22 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Academia Politécnica Naval</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13082,17 +13082,17 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>585599</v>
+        <v>2262.25</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3047-24-CM26</t>
+          <t>3431-9-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13112,22 +13112,22 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13143,17 +13143,17 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1999750.49</v>
+        <v>271.5</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3431-9-CM26</t>
+          <t>5052-91-SE26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13178,17 +13178,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13201,20 +13201,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>240000.63</v>
+        <v>202498.04</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5052-91-SE26</t>
+          <t>1681-85-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13239,12 +13243,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13262,24 +13266,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>179001319.63</v>
+        <v>33097.18</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1681-85-CM26</t>
+          <t>1681-84-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13330,17 +13330,17 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>29256770.23</v>
+        <v>44056.8</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1681-84-CM26</t>
+          <t>3382-21-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13365,17 +13365,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>65.311.270-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>CENTRO CLINICO MILITAR CONCEPCION</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13391,17 +13391,17 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>38944698.51</v>
+        <v>1131.27</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3382-21-CM26</t>
+          <t>1077908-22-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13416,27 +13416,27 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>65.311.270-K</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>CENTRO CLINICO MILITAR CONCEPCION</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13452,11 +13452,11 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>999999.6</v>
+        <v>31821.93</v>
       </c>
     </row>
     <row r="214">
@@ -13513,17 +13513,17 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>30699999.31</v>
+        <v>34729.85</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3474-78-CM26</t>
+          <t>1075337-6524-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13543,22 +13543,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13574,17 +13574,17 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>4939049.36</v>
+        <v>29414.6</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1075337-6524-CM26</t>
+          <t>1057480-344-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13604,22 +13604,22 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>Bienes y Servicios</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13635,17 +13635,17 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>26001500</v>
+        <v>56563.28</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1057480-344-CM26</t>
+          <t>1099899-10-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13665,22 +13665,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13696,17 +13696,17 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>50000000.45</v>
+        <v>7461.23</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1099899-10-CM26</t>
+          <t>1099899-11-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13757,17 +13757,17 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>6595470.4</v>
+        <v>1488.57</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1099899-11-CM26</t>
+          <t>4928-4-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13787,22 +13787,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13818,17 +13818,17 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1315845.48</v>
+        <v>61463.36</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1077908-22-CM26</t>
+          <t>1628-5-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13848,22 +13848,22 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13879,17 +13879,17 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>28129495.54</v>
+        <v>12443.92</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1628-5-CM26</t>
+          <t>1529-38-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13914,12 +13914,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13940,17 +13940,17 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>11000000.14</v>
+        <v>49909.82</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4928-4-CM26</t>
+          <t>2421-106-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13975,17 +13975,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Dirección de Administración de Salud Municipal</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14001,17 +14001,17 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>54331501.02</v>
+        <v>5652.72</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2421-106-CM26</t>
+          <t>3385-15-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14031,22 +14031,22 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14062,17 +14062,17 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>4996810</v>
+        <v>3489.95</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1465-57-CM26</t>
+          <t>1057385-23-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14097,17 +14097,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14123,17 +14123,17 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>12577714.64</v>
+        <v>20419.34</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3385-15-CM26</t>
+          <t>1079969-20-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14158,17 +14158,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14184,17 +14184,17 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3084999.97</v>
+        <v>535.2</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1057385-23-CM26</t>
+          <t>4968-156-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14219,17 +14219,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14245,17 +14245,17 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>18049999.37</v>
+        <v>4134.67</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1079969-20-CM26</t>
+          <t>4968-155-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14280,17 +14280,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14306,17 +14306,17 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>473099.55</v>
+        <v>1541.07</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4968-156-CM26</t>
+          <t>1590-17-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14341,17 +14341,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14367,17 +14367,17 @@
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3654906.5</v>
+        <v>1433.54</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4968-155-CM26</t>
+          <t>813685-8-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14428,17 +14428,17 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1362252.5</v>
+        <v>73685.97</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1590-17-CM26</t>
+          <t>1705-75-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14489,17 +14489,17 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1267200</v>
+        <v>22625.31</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>813685-8-CM26</t>
+          <t>1465-57-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14524,17 +14524,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14550,17 +14550,17 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>65135867.01</v>
+        <v>14228.74</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1705-75-CM26</t>
+          <t>5701-3-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -14585,17 +14585,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>Dirección General de Carabineros de Chile</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14611,133 +14611,11 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>20000001.08</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>1529-38-CM26</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2239-13-LR23</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>61.602.140-0</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M233" s="2" t="n">
-        <v>44118566.29</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>5701-3-CM26</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2239-13-LR23</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>60.505.000-K</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Dirección General de Carabineros de Chile</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M234" s="2" t="n">
-        <v>19211850.4</v>
+        <v>21733.71</v>
       </c>
     </row>
   </sheetData>
